--- a/backend/exports/bookings.xlsx
+++ b/backend/exports/bookings.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="127">
   <si>
     <t>Booking ID</t>
   </si>
@@ -365,6 +365,33 @@
   </si>
   <si>
     <t>27/6/2026, 6:25:23 pm</t>
+  </si>
+  <si>
+    <t>WT-228400</t>
+  </si>
+  <si>
+    <t>Nit Bhor</t>
+  </si>
+  <si>
+    <t>+919874562135</t>
+  </si>
+  <si>
+    <t>Dighi</t>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>Maharashtra</t>
+  </si>
+  <si>
+    <t>411058</t>
+  </si>
+  <si>
+    <t>19/9/2026</t>
+  </si>
+  <si>
+    <t>17/9/2026, 11:13:00 pm</t>
   </si>
 </sst>
 </file>
@@ -741,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1533,6 +1560,62 @@
         <v>117</v>
       </c>
     </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" t="s">
+        <v>121</v>
+      </c>
+      <c r="G18" t="s">
+        <v>122</v>
+      </c>
+      <c r="H18" t="s">
+        <v>123</v>
+      </c>
+      <c r="I18" t="s">
+        <v>124</v>
+      </c>
+      <c r="J18" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" t="s">
+        <v>125</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>15000</v>
+      </c>
+      <c r="N18" t="s">
+        <v>53</v>
+      </c>
+      <c r="O18">
+        <v>157</v>
+      </c>
+      <c r="P18">
+        <v>15000</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>82</v>
+      </c>
+      <c r="R18" t="s">
+        <v>126</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/backend/exports/bookings.xlsx
+++ b/backend/exports/bookings.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="137">
   <si>
     <t>Booking ID</t>
   </si>
@@ -392,6 +392,36 @@
   </si>
   <si>
     <t>17/9/2026, 11:13:00 pm</t>
+  </si>
+  <si>
+    <t>WT-656662</t>
+  </si>
+  <si>
+    <t>sczdczd zdsczdczs</t>
+  </si>
+  <si>
+    <t>scsz@gmail.com</t>
+  </si>
+  <si>
+    <t>+917894568532</t>
+  </si>
+  <si>
+    <t>sdsdsefsefse</t>
+  </si>
+  <si>
+    <t>sefsefsefesf</t>
+  </si>
+  <si>
+    <t>sefsefsef</t>
+  </si>
+  <si>
+    <t>562315</t>
+  </si>
+  <si>
+    <t>22/10/2026</t>
+  </si>
+  <si>
+    <t>7/10/2026, 8:17:34 pm</t>
   </si>
 </sst>
 </file>
@@ -768,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1616,6 +1646,62 @@
         <v>126</v>
       </c>
     </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" t="s">
+        <v>131</v>
+      </c>
+      <c r="G19" t="s">
+        <v>132</v>
+      </c>
+      <c r="H19" t="s">
+        <v>133</v>
+      </c>
+      <c r="I19" t="s">
+        <v>134</v>
+      </c>
+      <c r="J19" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" t="s">
+        <v>135</v>
+      </c>
+      <c r="L19">
+        <v>2</v>
+      </c>
+      <c r="M19">
+        <v>32000</v>
+      </c>
+      <c r="N19" t="s">
+        <v>53</v>
+      </c>
+      <c r="O19">
+        <v>335</v>
+      </c>
+      <c r="P19">
+        <v>32000</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>82</v>
+      </c>
+      <c r="R19" t="s">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/backend/exports/bookings.xlsx
+++ b/backend/exports/bookings.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="147">
   <si>
     <t>Booking ID</t>
   </si>
@@ -422,6 +422,36 @@
   </si>
   <si>
     <t>7/10/2026, 8:17:34 pm</t>
+  </si>
+  <si>
+    <t>WT-808282</t>
+  </si>
+  <si>
+    <t>aasasd asadasdad</t>
+  </si>
+  <si>
+    <t>ad@gmail.com</t>
+  </si>
+  <si>
+    <t>+918956412356</t>
+  </si>
+  <si>
+    <t>kjkdbvkjsdb</t>
+  </si>
+  <si>
+    <t>lbnsdjlvbvjlsb</t>
+  </si>
+  <si>
+    <t>ljbjlbjkb</t>
+  </si>
+  <si>
+    <t>852369</t>
+  </si>
+  <si>
+    <t>15/10/2026</t>
+  </si>
+  <si>
+    <t>8/10/2026, 11:03:03 am</t>
   </si>
 </sst>
 </file>
@@ -798,7 +828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1702,6 +1732,62 @@
         <v>136</v>
       </c>
     </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B20" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" t="s">
+        <v>140</v>
+      </c>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" t="s">
+        <v>141</v>
+      </c>
+      <c r="G20" t="s">
+        <v>142</v>
+      </c>
+      <c r="H20" t="s">
+        <v>143</v>
+      </c>
+      <c r="I20" t="s">
+        <v>144</v>
+      </c>
+      <c r="J20" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" t="s">
+        <v>145</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>14500</v>
+      </c>
+      <c r="N20" t="s">
+        <v>53</v>
+      </c>
+      <c r="O20">
+        <v>152</v>
+      </c>
+      <c r="P20">
+        <v>14500</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>82</v>
+      </c>
+      <c r="R20" t="s">
+        <v>146</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
